--- a/data/availability/projects/mountain-view/mountain-view-icity-october.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-icity-october.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mountain-view-icity-october</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1197,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1247,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1297,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1347,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1397,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1509,7 +1519,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1520,7 +1529,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1566,7 +1575,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1577,7 +1585,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1623,7 +1631,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1634,7 +1641,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1680,7 +1687,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1691,7 +1697,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1737,7 +1743,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1794,7 +1799,6 @@
       <c r="G7" t="n">
         <v>72.84</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1805,7 +1809,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1851,7 +1855,6 @@
       <c r="G8" t="n">
         <v>61.56</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1862,7 +1865,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1908,7 +1911,6 @@
       <c r="G9" t="n">
         <v>64.70999999999999</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1919,7 +1921,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1965,7 +1967,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2022,7 +2023,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2079,7 +2079,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2090,7 +2089,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2136,7 +2135,6 @@
       <c r="G13" t="n">
         <v>87.79000000000001</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2147,7 +2145,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2193,7 +2191,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2204,7 +2201,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2250,7 +2247,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2261,7 +2257,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2307,7 +2303,6 @@
       <c r="G16" t="n">
         <v>97.73</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2318,7 +2313,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2364,7 +2359,6 @@
       <c r="G17" t="n">
         <v>49.12</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2375,7 +2369,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2421,7 +2415,6 @@
       <c r="G18" t="n">
         <v>60.33</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2432,7 +2425,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2478,7 +2471,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2489,7 +2481,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2535,7 +2527,6 @@
       <c r="G20" t="n">
         <v>47.54</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2546,7 +2537,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2592,7 +2583,6 @@
       <c r="G21" t="n">
         <v>61.27</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2603,7 +2593,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2649,7 +2639,6 @@
       <c r="G22" t="n">
         <v>51.22</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2660,7 +2649,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2706,7 +2695,6 @@
       <c r="G23" t="n">
         <v>52.84</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2717,7 +2705,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2763,7 +2751,6 @@
       <c r="G24" t="n">
         <v>85.95</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2774,7 +2761,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2820,7 +2807,6 @@
       <c r="G25" t="n">
         <v>85.36</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2831,7 +2817,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2877,7 +2863,6 @@
       <c r="G26" t="n">
         <v>49.41</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2888,7 +2873,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2934,7 +2919,6 @@
       <c r="G27" t="n">
         <v>92.98</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2945,7 +2929,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2991,7 +2975,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3002,7 +2985,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3048,7 +3031,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3059,7 +3041,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3105,7 +3087,6 @@
       <c r="G30" t="n">
         <v>74.84999999999999</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3116,7 +3097,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3162,7 +3143,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3173,7 +3153,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3219,7 +3199,6 @@
       <c r="G32" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3230,7 +3209,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3276,7 +3255,6 @@
       <c r="G33" t="n">
         <v>78.03</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3287,7 +3265,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3333,7 +3311,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3344,7 +3321,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3390,7 +3367,6 @@
       <c r="G35" t="n">
         <v>108.79</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3401,7 +3377,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3447,7 +3423,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3458,7 +3433,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3504,7 +3479,6 @@
       <c r="G37" t="n">
         <v>77.45999999999999</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3515,7 +3489,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3561,7 +3535,6 @@
       <c r="G38" t="n">
         <v>56.6</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3572,7 +3545,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3618,7 +3591,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3629,7 +3601,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3675,7 +3647,6 @@
       <c r="G40" t="n">
         <v>62.3</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3686,7 +3657,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3732,7 +3703,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3743,7 +3713,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3789,7 +3759,6 @@
       <c r="G42" t="n">
         <v>72.91</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3800,7 +3769,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3846,7 +3815,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3857,7 +3825,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3903,7 +3871,6 @@
       <c r="G44" t="n">
         <v>68.93000000000001</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3914,7 +3881,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3960,7 +3927,6 @@
       <c r="G45" t="n">
         <v>66.75</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3971,7 +3937,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4017,7 +3983,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4028,7 +3993,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4074,7 +4039,6 @@
       <c r="G47" t="n">
         <v>64.09999999999999</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4085,7 +4049,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4131,7 +4095,6 @@
       <c r="G48" t="n">
         <v>53.43</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4142,7 +4105,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4188,7 +4151,6 @@
       <c r="G49" t="n">
         <v>0</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4199,7 +4161,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4245,7 +4207,6 @@
       <c r="G50" t="n">
         <v>0</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4256,7 +4217,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4302,7 +4263,6 @@
       <c r="G51" t="n">
         <v>52.22</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4313,7 +4273,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4359,7 +4319,6 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4370,7 +4329,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4416,7 +4375,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4427,7 +4385,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4473,7 +4431,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4484,7 +4441,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4530,7 +4487,6 @@
       <c r="G55" t="n">
         <v>17.15</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4541,7 +4497,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4587,7 +4543,6 @@
       <c r="G56" t="n">
         <v>29.91</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4598,7 +4553,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4644,7 +4599,6 @@
       <c r="G57" t="n">
         <v>101.51</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4655,7 +4609,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4701,7 +4655,6 @@
       <c r="G58" t="n">
         <v>0</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4712,7 +4665,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4758,7 +4711,6 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4769,7 +4721,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4815,7 +4767,6 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4826,7 +4777,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4872,7 +4823,6 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4883,7 +4833,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4929,7 +4879,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4940,7 +4889,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4986,7 +4935,6 @@
       <c r="G63" t="n">
         <v>43.56</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4997,7 +4945,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5043,7 +4991,6 @@
       <c r="G64" t="n">
         <v>145</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5100,7 +5047,6 @@
       <c r="G65" t="n">
         <v>238</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5157,7 +5103,6 @@
       <c r="G66" t="n">
         <v>122.93</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5168,7 +5113,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>OFF PLAN - 2</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5214,7 +5159,6 @@
       <c r="G67" t="n">
         <v>273</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5225,7 +5169,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5271,7 +5215,6 @@
       <c r="G68" t="n">
         <v>226</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5282,7 +5225,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5328,7 +5271,6 @@
       <c r="G69" t="n">
         <v>226</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5339,7 +5281,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5385,7 +5327,6 @@
       <c r="G70" t="n">
         <v>252</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5396,7 +5337,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5442,7 +5383,6 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5453,7 +5393,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5499,7 +5439,6 @@
       <c r="G72" t="n">
         <v>22</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5510,7 +5449,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5556,7 +5495,6 @@
       <c r="G73" t="n">
         <v>0</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5567,7 +5505,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5613,7 +5551,6 @@
       <c r="G74" t="n">
         <v>0</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5624,7 +5561,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5670,7 +5607,6 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5681,7 +5617,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5727,7 +5663,6 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5738,7 +5673,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5784,7 +5719,6 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5795,7 +5729,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5841,7 +5775,6 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5852,7 +5785,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5898,7 +5831,6 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5909,7 +5841,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5955,7 +5887,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5966,7 +5897,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6012,7 +5943,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6023,7 +5953,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6069,7 +5999,6 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6080,7 +6009,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6126,7 +6055,6 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6137,7 +6065,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6183,7 +6111,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6194,7 +6121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6240,7 +6167,6 @@
       <c r="G85" t="n">
         <v>0</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6251,7 +6177,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6297,7 +6223,6 @@
       <c r="G86" t="n">
         <v>0</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6308,7 +6233,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6354,7 +6279,6 @@
       <c r="G87" t="n">
         <v>0</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6365,7 +6289,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6411,7 +6335,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6422,7 +6345,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6468,7 +6391,6 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6479,7 +6401,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6525,7 +6447,6 @@
       <c r="G90" t="n">
         <v>22</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6536,7 +6457,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6582,7 +6503,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6593,7 +6513,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6639,7 +6559,6 @@
       <c r="G92" t="n">
         <v>135</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6650,7 +6569,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6696,7 +6615,6 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6707,7 +6625,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6753,7 +6671,6 @@
       <c r="G94" t="n">
         <v>116</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6764,7 +6681,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6810,7 +6727,6 @@
       <c r="G95" t="n">
         <v>22</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6821,7 +6737,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6867,7 +6783,6 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6878,7 +6793,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6924,7 +6839,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6935,7 +6849,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6981,7 +6895,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6992,7 +6905,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7038,7 +6951,6 @@
       <c r="G99" t="n">
         <v>135</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7049,7 +6961,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7095,7 +7007,6 @@
       <c r="G100" t="n">
         <v>60</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7106,7 +7017,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7152,7 +7063,6 @@
       <c r="G101" t="n">
         <v>137</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7163,7 +7073,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7209,7 +7119,6 @@
       <c r="G102" t="n">
         <v>22</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7220,7 +7129,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7266,7 +7175,6 @@
       <c r="G103" t="n">
         <v>35</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7277,7 +7185,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7323,7 +7231,6 @@
       <c r="G104" t="n">
         <v>137</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7334,7 +7241,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7380,7 +7287,6 @@
       <c r="G105" t="n">
         <v>35</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7391,7 +7297,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7437,7 +7343,6 @@
       <c r="G106" t="n">
         <v>22</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7448,7 +7353,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7494,7 +7399,6 @@
       <c r="G107" t="n">
         <v>135</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7505,7 +7409,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7551,7 +7455,6 @@
       <c r="G108" t="n">
         <v>22</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7562,7 +7465,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7608,7 +7511,6 @@
       <c r="G109" t="n">
         <v>35</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7619,7 +7521,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7665,7 +7567,6 @@
       <c r="G110" t="n">
         <v>0</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7676,7 +7577,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7722,7 +7623,6 @@
       <c r="G111" t="n">
         <v>0</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7733,7 +7633,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7779,7 +7679,6 @@
       <c r="G112" t="n">
         <v>135</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7790,7 +7689,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7836,7 +7735,6 @@
       <c r="G113" t="n">
         <v>60</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7847,7 +7745,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7893,7 +7791,6 @@
       <c r="G114" t="n">
         <v>35</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7904,7 +7801,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7950,7 +7847,6 @@
       <c r="G115" t="n">
         <v>22</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7961,7 +7857,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8007,7 +7903,6 @@
       <c r="G116" t="n">
         <v>0</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8018,7 +7913,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8064,7 +7959,6 @@
       <c r="G117" t="n">
         <v>0</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8075,7 +7969,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8121,7 +8015,6 @@
       <c r="G118" t="n">
         <v>60</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8132,7 +8025,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8178,7 +8071,6 @@
       <c r="G119" t="n">
         <v>224</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8189,7 +8081,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8235,7 +8127,6 @@
       <c r="G120" t="n">
         <v>0</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8246,7 +8137,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8292,7 +8183,6 @@
       <c r="G121" t="n">
         <v>227</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8303,7 +8193,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8349,7 +8239,6 @@
       <c r="G122" t="n">
         <v>60</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8360,7 +8249,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8406,7 +8295,6 @@
       <c r="G123" t="n">
         <v>0</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8417,7 +8305,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -8463,7 +8351,6 @@
       <c r="G124" t="n">
         <v>0</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8474,7 +8361,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -8520,7 +8407,6 @@
       <c r="G125" t="n">
         <v>60</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8531,7 +8417,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8577,7 +8463,6 @@
       <c r="G126" t="n">
         <v>135</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8588,7 +8473,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -8634,7 +8519,6 @@
       <c r="G127" t="n">
         <v>22</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8645,7 +8529,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -8691,7 +8575,6 @@
       <c r="G128" t="n">
         <v>35</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8702,7 +8585,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8748,7 +8631,6 @@
       <c r="G129" t="n">
         <v>0</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8759,7 +8641,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -8805,7 +8687,6 @@
       <c r="G130" t="n">
         <v>22</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8816,7 +8697,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8862,7 +8743,6 @@
       <c r="G131" t="n">
         <v>137</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8873,7 +8753,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -8919,7 +8799,6 @@
       <c r="G132" t="n">
         <v>22</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8930,7 +8809,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8976,7 +8855,6 @@
       <c r="G133" t="n">
         <v>0</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8987,7 +8865,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9033,7 +8911,6 @@
       <c r="G134" t="n">
         <v>0</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9044,7 +8921,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9090,7 +8967,6 @@
       <c r="G135" t="n">
         <v>137</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9101,7 +8977,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9147,7 +9023,6 @@
       <c r="G136" t="n">
         <v>22</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9158,7 +9033,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -9204,7 +9079,6 @@
       <c r="G137" t="n">
         <v>0</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9215,7 +9089,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9261,7 +9135,6 @@
       <c r="G138" t="n">
         <v>137</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9272,7 +9145,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9318,7 +9191,6 @@
       <c r="G139" t="n">
         <v>22</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9329,7 +9201,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -9375,7 +9247,6 @@
       <c r="G140" t="n">
         <v>0</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9386,7 +9257,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -9432,7 +9303,6 @@
       <c r="G141" t="n">
         <v>138</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9443,7 +9313,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -9489,7 +9359,6 @@
       <c r="G142" t="n">
         <v>22</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9500,7 +9369,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -9546,7 +9415,6 @@
       <c r="G143" t="n">
         <v>135</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9557,7 +9425,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9603,7 +9471,6 @@
       <c r="G144" t="n">
         <v>22</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9614,7 +9481,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -9660,7 +9527,6 @@
       <c r="G145" t="n">
         <v>92</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9671,7 +9537,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -9717,7 +9583,6 @@
       <c r="G146" t="n">
         <v>135</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9728,7 +9593,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9774,7 +9639,6 @@
       <c r="G147" t="n">
         <v>93</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9785,7 +9649,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -9831,7 +9695,6 @@
       <c r="G148" t="n">
         <v>22</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9842,7 +9705,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -9888,7 +9751,6 @@
       <c r="G149" t="n">
         <v>138</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9899,7 +9761,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -9945,7 +9807,6 @@
       <c r="G150" t="n">
         <v>150</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9956,7 +9817,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -10002,7 +9863,6 @@
       <c r="G151" t="n">
         <v>157</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10013,7 +9873,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -10059,7 +9919,6 @@
       <c r="G152" t="n">
         <v>69</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10070,7 +9929,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -10116,7 +9975,6 @@
       <c r="G153" t="n">
         <v>22</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10127,7 +9985,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10173,7 +10031,6 @@
       <c r="G154" t="n">
         <v>69</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10184,7 +10041,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10230,7 +10087,6 @@
       <c r="G155" t="n">
         <v>151</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10241,7 +10097,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -10287,7 +10143,6 @@
       <c r="G156" t="n">
         <v>95</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10298,7 +10153,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10344,7 +10199,6 @@
       <c r="G157" t="n">
         <v>22</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10355,7 +10209,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -10401,7 +10255,6 @@
       <c r="G158" t="n">
         <v>0</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10412,7 +10265,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -10458,7 +10311,6 @@
       <c r="G159" t="n">
         <v>154</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10469,7 +10321,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10515,7 +10367,6 @@
       <c r="G160" t="n">
         <v>65</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10526,7 +10377,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -10572,7 +10423,6 @@
       <c r="G161" t="n">
         <v>22</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10583,7 +10433,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10629,7 +10479,6 @@
       <c r="G162" t="n">
         <v>85</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10640,7 +10489,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -10686,7 +10535,6 @@
       <c r="G163" t="n">
         <v>0</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10697,7 +10545,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10743,7 +10591,6 @@
       <c r="G164" t="n">
         <v>65</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10754,7 +10601,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10800,7 +10647,6 @@
       <c r="G165" t="n">
         <v>150</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10811,7 +10657,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -10857,7 +10703,6 @@
       <c r="G166" t="n">
         <v>88</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10868,7 +10713,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -10914,7 +10759,6 @@
       <c r="G167" t="n">
         <v>22</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10925,7 +10769,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -10971,7 +10815,6 @@
       <c r="G168" t="n">
         <v>0</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10982,7 +10825,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11028,7 +10871,6 @@
       <c r="G169" t="n">
         <v>61</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11039,7 +10881,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -11085,7 +10927,6 @@
       <c r="G170" t="n">
         <v>22</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11096,7 +10937,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -11142,7 +10983,6 @@
       <c r="G171" t="n">
         <v>137</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11153,7 +10993,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -11199,7 +11039,6 @@
       <c r="G172" t="n">
         <v>88</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11210,7 +11049,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11256,7 +11095,6 @@
       <c r="G173" t="n">
         <v>137</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11267,7 +11105,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11313,7 +11151,6 @@
       <c r="G174" t="n">
         <v>22</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11324,7 +11161,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -11370,7 +11207,6 @@
       <c r="G175" t="n">
         <v>22</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11381,7 +11217,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -11427,7 +11263,6 @@
       <c r="G176" t="n">
         <v>22</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11438,7 +11273,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11484,7 +11319,6 @@
       <c r="G177" t="n">
         <v>0</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11495,7 +11329,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -11541,7 +11375,6 @@
       <c r="G178" t="n">
         <v>132</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11552,7 +11385,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -11598,7 +11431,6 @@
       <c r="G179" t="n">
         <v>22</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11609,7 +11441,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11655,7 +11487,6 @@
       <c r="G180" t="n">
         <v>22</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11666,7 +11497,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -11712,7 +11543,6 @@
       <c r="G181" t="n">
         <v>171</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11723,7 +11553,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11769,7 +11599,6 @@
       <c r="G182" t="n">
         <v>22</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11780,7 +11609,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -11826,7 +11655,6 @@
       <c r="G183" t="n">
         <v>136</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11837,7 +11665,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11883,7 +11711,6 @@
       <c r="G184" t="n">
         <v>22</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11894,7 +11721,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -11940,7 +11767,6 @@
       <c r="G185" t="n">
         <v>0</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11951,7 +11777,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -11997,7 +11823,6 @@
       <c r="G186" t="n">
         <v>135</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12008,7 +11833,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12054,7 +11879,6 @@
       <c r="G187" t="n">
         <v>100</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12065,7 +11889,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -12111,7 +11935,6 @@
       <c r="G188" t="n">
         <v>0</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12122,7 +11945,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -12168,7 +11991,6 @@
       <c r="G189" t="n">
         <v>0</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12179,7 +12001,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12225,7 +12047,6 @@
       <c r="G190" t="n">
         <v>0</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12236,7 +12057,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -12282,7 +12103,6 @@
       <c r="G191" t="n">
         <v>0</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12293,7 +12113,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -12339,7 +12159,6 @@
       <c r="G192" t="n">
         <v>0</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12350,7 +12169,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -12396,7 +12215,6 @@
       <c r="G193" t="n">
         <v>0</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12407,7 +12225,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12453,7 +12271,6 @@
       <c r="G194" t="n">
         <v>113</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12464,7 +12281,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -12510,7 +12327,6 @@
       <c r="G195" t="n">
         <v>0</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12521,7 +12337,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12567,7 +12383,6 @@
       <c r="G196" t="n">
         <v>0</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12578,7 +12393,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -12624,7 +12439,6 @@
       <c r="G197" t="n">
         <v>146</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12635,7 +12449,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -12681,7 +12495,6 @@
       <c r="G198" t="n">
         <v>0</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12692,7 +12505,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -12738,7 +12551,6 @@
       <c r="G199" t="n">
         <v>0</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12749,7 +12561,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -12795,7 +12607,6 @@
       <c r="G200" t="n">
         <v>0</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12806,7 +12617,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -12852,7 +12663,6 @@
       <c r="G201" t="n">
         <v>146</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12863,7 +12673,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>OFF PLAN - 4.5</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">

--- a/data/availability/projects/mountain-view/mountain-view-icity-october.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-icity-october.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -614,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -664,7 +664,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -764,7 +764,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -864,7 +864,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -914,7 +914,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Park Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -964,7 +964,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Park Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I-Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I-Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garden Millennial</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3231,7 +3231,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Park Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>I-Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sky Loft</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Park Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>I-Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>I-Villa</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Garden Millennial</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Garden Millennial</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Garden Millennial</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Garden Millennial</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7319,7 +7319,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8383,7 +8383,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9615,7 +9615,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10119,7 +10119,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10287,7 +10287,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11071,7 +11071,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11519,7 +11519,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12583,7 +12583,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>I-Villa 3</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Park Side House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
